--- a/Output/PowerPoint_Figures/Fig_3/Fig_3d_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_3/Fig_3d_data.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOOCV_Full" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOOCV_Plotted" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOOCV_Strip_Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,17 +461,17 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>N_features</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Confusion_Matrix</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Plot_Filter</t>
         </is>
       </c>
     </row>
@@ -504,25 +503,23 @@
       <c r="G2" t="n">
         <v>25</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>22</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>[[4, 7], [4, 10]]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -531,42 +528,40 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Arrhythmia</t>
+          <t>heart_damage</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SVM_RBF</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.52</v>
+        <v>0.72</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4415584415584415</v>
+        <v>0.4599999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>25</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>[[3, 8], [4, 10]]</t>
-        </is>
+      <c r="H3" t="n">
+        <v>22</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[1, 4], [3, 17]]</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -575,46 +570,44 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Arrhythmia</t>
+          <t>Concern_Binary</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>0.6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5584415584415585</v>
+        <v>0.6566666666666667</v>
       </c>
       <c r="G4" t="n">
         <v>25</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>[[3, 8], [2, 12]]</t>
-        </is>
+      <c r="H4" t="n">
+        <v>22</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[7, 3], [7, 8]]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dual_exponential</t>
+          <t>bivariate_gaussian</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -624,41 +617,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GaussianNB</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.48</v>
+        <v>0.68</v>
       </c>
       <c r="F5" t="n">
-        <v>0.435064935064935</v>
+        <v>0.6233766233766234</v>
       </c>
       <c r="G5" t="n">
         <v>25</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>[[4, 7], [6, 8]]</t>
-        </is>
+      <c r="H5" t="n">
+        <v>26</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[7, 4], [4, 10]]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dual_exponential</t>
+          <t>bivariate_gaussian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -668,129 +659,123 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="F6" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="G6" t="n">
         <v>25</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>[[1, 4], [7, 13]]</t>
-        </is>
+      <c r="H6" t="n">
+        <v>26</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[0, 5], [3, 17]]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dual_exponential</t>
+          <t>bivariate_gaussian</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>heart_damage</t>
+          <t>Concern_Binary</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SVM_RBF</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1699999999999999</v>
+        <v>0.4433333333333333</v>
       </c>
       <c r="G7" t="n">
         <v>25</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>[[0, 5], [3, 17]]</t>
-        </is>
+      <c r="H7" t="n">
+        <v>26</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[3, 7], [6, 9]]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dual_exponential</t>
+          <t>gaussian_hill_hybrid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>heart_damage</t>
+          <t>Arrhythmia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>0.76</v>
       </c>
       <c r="F8" t="n">
-        <v>0.435</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>[[0, 5], [1, 19]]</t>
-        </is>
+      <c r="H8" t="n">
+        <v>20</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[8, 3], [3, 11]]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dual_exponential</t>
+          <t>gaussian_hill_hybrid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -804,37 +789,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4599999999999999</v>
+        <v>0.6299999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>25</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>[[1, 4], [3, 17]]</t>
-        </is>
+      <c r="H9" t="n">
+        <v>20</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[3, 2], [6, 14]]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dual_exponential</t>
+          <t>gaussian_hill_hybrid</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -844,129 +827,123 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4733333333333333</v>
+        <v>0.4733333333333334</v>
       </c>
       <c r="G10" t="n">
         <v>25</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>[[2, 8], [5, 10]]</t>
-        </is>
+      <c r="H10" t="n">
+        <v>20</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[3, 7], [5, 10]]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>dual_exponential</t>
+          <t>modified_hill_hormesis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Concern_Binary</t>
+          <t>Arrhythmia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SVM_RBF</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3066666666666667</v>
+        <v>0.6753246753246753</v>
       </c>
       <c r="G11" t="n">
         <v>25</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>[[2, 8], [3, 12]]</t>
-        </is>
+      <c r="H11" t="n">
+        <v>18</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[9, 2], [5, 9]]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>dual_exponential</t>
+          <t>modified_hill_hormesis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Concern_Binary</t>
+          <t>heart_damage</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="F12" t="n">
-        <v>0.39</v>
+        <v>0.3399999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>[[1, 9], [2, 13]]</t>
-        </is>
+      <c r="H12" t="n">
+        <v>18</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[1, 4], [9, 11]]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dual_exponential</t>
+          <t>modified_hill_hormesis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -980,37 +957,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6</v>
+        <v>0.36</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6566666666666667</v>
+        <v>0.32</v>
       </c>
       <c r="G13" t="n">
         <v>25</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>[[7, 3], [7, 8]]</t>
-        </is>
+      <c r="H13" t="n">
+        <v>18</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[7, 3], [13, 2]]</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>modified_hill_hormesis</t>
+          <t>gaussian_ridge</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1024,125 +999,119 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.72</v>
+        <v>0.52</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6753246753246753</v>
+        <v>0.6883116883116883</v>
       </c>
       <c r="G14" t="n">
         <v>25</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>[[9, 2], [5, 9]]</t>
-        </is>
+      <c r="H14" t="n">
+        <v>22</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[6, 5], [7, 7]]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>modified_hill_hormesis</t>
+          <t>gaussian_ridge</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arrhythmia</t>
+          <t>heart_damage</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SVM_RBF</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>0.68</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5129870129870129</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>25</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>[[6, 5], [3, 11]]</t>
-        </is>
+      <c r="H15" t="n">
+        <v>22</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[2, 3], [5, 15]]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>modified_hill_hormesis</t>
+          <t>gaussian_ridge</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Arrhythmia</t>
+          <t>Concern_Binary</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.32</v>
       </c>
       <c r="G16" t="n">
         <v>25</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>[[6, 5], [3, 11]]</t>
-        </is>
+      <c r="H16" t="n">
+        <v>22</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[4, 6], [7, 8]]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>modified_hill_hormesis</t>
+          <t>adaptive_response</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1152,41 +1121,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>GaussianNB</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6103896103896104</v>
+        <v>0.6493506493506493</v>
       </c>
       <c r="G17" t="n">
         <v>25</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>[[6, 5], [2, 12]]</t>
-        </is>
+      <c r="H17" t="n">
+        <v>12</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[6, 5], [4, 10]]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>modified_hill_hormesis</t>
+          <t>adaptive_response</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1196,129 +1163,123 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="F18" t="n">
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
       <c r="G18" t="n">
         <v>25</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>[[0, 5], [10, 10]]</t>
-        </is>
+      <c r="H18" t="n">
+        <v>12</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[0, 5], [4, 16]]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>modified_hill_hormesis</t>
+          <t>adaptive_response</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>heart_damage</t>
+          <t>Concern_Binary</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SVM_RBF</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5399999999999999</v>
+        <v>0.5866666666666667</v>
       </c>
       <c r="G19" t="n">
         <v>25</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>[[1, 4], [3, 17]]</t>
-        </is>
+      <c r="H19" t="n">
+        <v>12</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[6, 4], [6, 9]]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>biphasic_response</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Arrhythmia</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="G20" t="n">
+        <v>25</v>
+      </c>
+      <c r="H20" t="n">
         <v>18</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>modified_hill_hormesis</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>heart_damage</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G20" t="n">
-        <v>25</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>[[0, 5], [1, 19]]</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[4, 7], [8, 6]]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>modified_hill_hormesis</t>
+          <t>biphasic_response</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1332,37 +1293,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3399999999999999</v>
+        <v>0.23</v>
       </c>
       <c r="G21" t="n">
         <v>25</v>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>[[1, 4], [9, 11]]</t>
-        </is>
+      <c r="H21" t="n">
+        <v>18</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[1, 4], [12, 8]]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>modified_hill_hormesis</t>
+          <t>biphasic_response</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1372,129 +1331,123 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6133333333333333</v>
+        <v>0.4599999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>25</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>[[6, 4], [7, 8]]</t>
-        </is>
+      <c r="H22" t="n">
+        <v>18</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[8, 2], [12, 3]]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>modified_hill_hormesis</t>
+          <t>cumulative_exposure</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Concern_Binary</t>
+          <t>Arrhythmia</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SVM_RBF</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5</v>
+        <v>0.6233766233766234</v>
       </c>
       <c r="G23" t="n">
         <v>25</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>[[5, 5], [4, 11]]</t>
-        </is>
+      <c r="H23" t="n">
+        <v>10</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[7, 4], [4, 10]]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>modified_hill_hormesis</t>
+          <t>cumulative_exposure</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Concern_Binary</t>
+          <t>heart_damage</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4933333333333333</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>25</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>[[3, 7], [2, 13]]</t>
-        </is>
+      <c r="H24" t="n">
+        <v>10</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[3, 2], [13, 7]]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>modified_hill_hormesis</t>
+          <t>cumulative_exposure</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1508,37 +1461,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.32</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="G25" t="n">
         <v>25</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>[[7, 3], [13, 2]]</t>
-        </is>
+      <c r="H25" t="n">
+        <v>10</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[3, 7], [1, 14]]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>pkpd_elimination</t>
+          <t>recovery_model</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1552,125 +1503,119 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7792207792207793</v>
+        <v>0.7207792207792207</v>
       </c>
       <c r="G26" t="n">
         <v>25</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>[[8, 3], [4, 10]]</t>
-        </is>
+      <c r="H26" t="n">
+        <v>8</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[8, 3], [5, 9]]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>pkpd_elimination</t>
+          <t>recovery_model</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Arrhythmia</t>
+          <t>heart_damage</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SVM_RBF</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.52</v>
+        <v>0.36</v>
       </c>
       <c r="F27" t="n">
-        <v>0.564935064935065</v>
+        <v>0.3199999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>25</v>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>[[6, 5], [7, 7]]</t>
-        </is>
+      <c r="H27" t="n">
+        <v>8</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[2, 3], [13, 7]]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>pkpd_elimination</t>
+          <t>recovery_model</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Arrhythmia</t>
+          <t>Concern_Binary</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.76</v>
+        <v>0.44</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7954545454545454</v>
+        <v>0.3933333333333333</v>
       </c>
       <c r="G28" t="n">
         <v>25</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>[[8, 3], [3, 11]]</t>
-        </is>
+      <c r="H28" t="n">
+        <v>8</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[8, 2], [12, 3]]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>pkpd_elimination</t>
+          <t>modified_hill_simple</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1680,41 +1625,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GaussianNB</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5844155844155844</v>
+        <v>0.7207792207792209</v>
       </c>
       <c r="G29" t="n">
         <v>25</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>[[6, 5], [5, 9]]</t>
-        </is>
+      <c r="H29" t="n">
+        <v>12</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[8, 3], [5, 9]]</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>28</v>
+        <v>115</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>pkpd_elimination</t>
+          <t>modified_hill_simple</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1724,81 +1667,77 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.6</v>
+        <v>0.72</v>
       </c>
       <c r="F30" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="G30" t="n">
         <v>25</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>[[1, 4], [6, 14]]</t>
-        </is>
+      <c r="H30" t="n">
+        <v>12</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[1, 4], [3, 17]]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>pkpd_elimination</t>
+          <t>modified_hill_simple</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>heart_damage</t>
+          <t>Concern_Binary</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SVM_RBF</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="F31" t="n">
-        <v>0.75</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="G31" t="n">
         <v>25</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>[[2, 3], [2, 18]]</t>
-        </is>
+      <c r="H31" t="n">
+        <v>12</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[8, 2], [4, 11]]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1807,42 +1746,40 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>heart_damage</t>
+          <t>Arrhythmia</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="F32" t="n">
-        <v>0.58</v>
+        <v>0.7792207792207793</v>
       </c>
       <c r="G32" t="n">
         <v>25</v>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>[[0, 5], [1, 19]]</t>
-        </is>
+      <c r="H32" t="n">
+        <v>14</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[8, 3], [4, 10]]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1868,25 +1805,23 @@
       <c r="G33" t="n">
         <v>25</v>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" t="n">
+        <v>14</v>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>[[2, 3], [2, 18]]</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1900,129 +1835,123 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.6</v>
+        <v>0.76</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5133333333333334</v>
+        <v>0.8866666666666667</v>
       </c>
       <c r="G34" t="n">
         <v>25</v>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>[[4, 6], [4, 11]]</t>
-        </is>
+      <c r="H34" t="n">
+        <v>14</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[6, 4], [2, 13]]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>pkpd_elimination</t>
+          <t>hormesis_v0</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Concern_Binary</t>
+          <t>Arrhythmia</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SVM_RBF</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.72</v>
+        <v>0.52</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="G35" t="n">
         <v>25</v>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>[[6, 4], [3, 12]]</t>
-        </is>
+      <c r="H35" t="n">
+        <v>18</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[6, 5], [7, 7]]</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>pkpd_elimination</t>
+          <t>hormesis_v0</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Concern_Binary</t>
+          <t>heart_damage</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.68</v>
+        <v>0.44</v>
       </c>
       <c r="F36" t="n">
-        <v>0.76</v>
+        <v>0.2099999999999999</v>
       </c>
       <c r="G36" t="n">
         <v>25</v>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>[[5, 5], [3, 12]]</t>
-        </is>
+      <c r="H36" t="n">
+        <v>18</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[1, 4], [10, 10]]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>pkpd_elimination</t>
+          <t>hormesis_v0</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2036,384 +1965,25 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.76</v>
+        <v>0.4</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8866666666666667</v>
+        <v>0.62</v>
       </c>
       <c r="G37" t="n">
         <v>25</v>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>[[6, 4], [2, 13]]</t>
-        </is>
+      <c r="H37" t="n">
+        <v>18</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\loocv_results.csv</t>
+          <t>[[7, 3], [12, 3]]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>RandomForest model, 3 targets, 3 equations</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Equation</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>AUC</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>N_samples</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Confusion_Matrix</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>dual_exponential</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Arrhythmia</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.5584415584415585</v>
-      </c>
-      <c r="G2" t="n">
-        <v>25</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>[[3, 8], [2, 12]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>dual_exponential</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>heart_damage</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="G3" t="n">
-        <v>25</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>[[0, 5], [1, 19]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>dual_exponential</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Concern_Binary</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="G4" t="n">
-        <v>25</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>[[1, 9], [2, 13]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>modified_hill_hormesis</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Arrhythmia</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.6785714285714286</v>
-      </c>
-      <c r="G5" t="n">
-        <v>25</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>[[6, 5], [3, 11]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>modified_hill_hormesis</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>heart_damage</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G6" t="n">
-        <v>25</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>[[0, 5], [1, 19]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>modified_hill_hormesis</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Concern_Binary</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.4933333333333333</v>
-      </c>
-      <c r="G7" t="n">
-        <v>25</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>[[3, 7], [2, 13]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>pkpd_elimination</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Arrhythmia</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.7954545454545454</v>
-      </c>
-      <c r="G8" t="n">
-        <v>25</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>[[8, 3], [3, 11]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>pkpd_elimination</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>heart_damage</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>[[0, 5], [1, 19]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>pkpd_elimination</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Concern_Binary</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="G10" t="n">
-        <v>25</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>[[5, 5], [3, 12]]</t>
+          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
         </is>
       </c>
     </row>

--- a/Output/PowerPoint_Figures/Fig_3/Fig_3d_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_3/Fig_3d_data.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,54 +417,54 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>AUC</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>N_samples</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>N_features</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Confusion_Matrix</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,12 +501,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -555,12 +543,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>11</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -597,12 +585,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>12</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -639,12 +627,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>19</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -681,12 +669,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>23</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -723,12 +711,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>24</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -765,12 +753,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>31</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -807,12 +795,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>35</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -849,12 +837,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>36</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -891,12 +879,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>43</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -933,12 +921,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>47</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -975,12 +963,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>48</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1017,12 +1005,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>55</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1059,12 +1047,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>59</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1101,12 +1089,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>60</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1143,12 +1131,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>67</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1185,12 +1173,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>71</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1227,12 +1215,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>72</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1269,12 +1257,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>79</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1311,12 +1299,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>83</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1353,12 +1341,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>84</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1395,12 +1383,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>91</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1437,12 +1425,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>95</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1479,12 +1467,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>96</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1521,12 +1509,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>103</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1563,12 +1551,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>107</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1605,12 +1593,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>108</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1647,12 +1635,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>115</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1689,12 +1677,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>119</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1731,12 +1719,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>120</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1773,12 +1761,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>127</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1815,12 +1803,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>131</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1857,12 +1845,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>132</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1899,12 +1887,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>139</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -1941,12 +1929,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>143</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -1983,7 +1971,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\All_Equations_LOOCV\loocv_all_equations.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/All_Equations_LOOCV/loocv_all_equations.csv</t>
         </is>
       </c>
     </row>

--- a/Output/PowerPoint_Figures/Fig_3/Fig_3d_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_3/Fig_3d_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOOCV_Strip_Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LOOCV_Strip_Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Output/PowerPoint_Figures/Fig_3/Fig_3d_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_3/Fig_3d_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="LOOCV_Strip_Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOOCV_Strip_Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
